--- a/backend/backups/category7_domestic_help_cooking_FINAL.xlsx
+++ b/backend/backups/category7_domestic_help_cooking_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,615 +425,668 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40b63594-5545-5186-8c79-12e95f135bbd</t>
+          <t>24122f06-e74f-584d-83f0-8e07ffcc566e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 1</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Evening Snack &amp; High-Tea Cook</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>600</v>
+        <v>1999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Cook visiting daily at 4 PM to prepare fresh tea, pakoras, samosas, or sandwiches.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Evening Snack &amp; High-Tea Cook procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Evening Snack &amp; High-Tea Cook procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.846588+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.846588+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Evening Snack &amp; High-Tea Cook take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a1ce921c-1580-5cc8-89c0-0c404e03620d</t>
+          <t>21214b3e-e44e-5cd7-9cec-1b17f71316af</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 2</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Healthy Fitness Meal Prep Cook (Diet Specific)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>700</v>
+        <v>3999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Cook preparing low-oil, high-protein keto, salad, grilled chicken, or vegan customized meal plans.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Healthy Fitness Meal Prep Cook (Diet Specific) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Healthy Fitness Meal Prep Cook (Diet Specific) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.851654+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.851654+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Healthy Fitness Meal Prep Cook (Diet Specific) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>c53f41db-6864-5098-962e-5b8cd6d01533</t>
+          <t>2527c933-3089-5fe2-aacd-fa3ae48c78f0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 3</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Jain Pure Vegetarian Home Cook</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>3699</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Strictly onion-free, garlic-free pure vegetarian food preparation following Jain dietary rules.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Jain Pure Vegetarian Home Cook procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Jain Pure Vegetarian Home Cook procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.854915+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.854915+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Jain Pure Vegetarian Home Cook take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>50708bc9-4abb-563d-92a7-3266f4eb4213</t>
+          <t>2aa7c0cc-9967-5a63-aa3e-d6f3b80b8304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 4</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Kids School Tiffin &amp; Breakfast Specialist</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>900</v>
+        <v>2199</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Early morning cook preparing nutritious, creative tiffin meals for school children.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Kids School Tiffin &amp; Breakfast Specialist procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Kids School Tiffin &amp; Breakfast Specialist procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.857639+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.857639+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Kids School Tiffin &amp; Breakfast Specialist take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6f70225a-efcb-50ac-a11a-3abf2809908d</t>
+          <t>40735bdb-7e84-561a-bd66-3cac217acc77</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 5</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Monthly Full-Time Resident House Cook</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1000</v>
+        <v>9999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Dedicated full-day cook managing grocery inventory, meal planning, and 3 meals daily.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Monthly Full-Time Resident House Cook procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Monthly Full-Time Resident House Cook procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.860484+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.860484+00:00</t>
+          <t>[{'answer': 'The session typically takes around 480 minutes.', 'question': 'How long does Monthly Full-Time Resident House Cook take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ab5ac2a7-edc9-5443-8456-b2f6c4ed5da9</t>
+          <t>01d0d750-e8bf-58e1-bd31-8ff6ad447a4a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 6</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>North Indian Meal Home Cook (Daily 2 Meals)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1100</v>
+        <v>3499</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Experienced cook preparing fresh roti, sabzi, dal, and rice tailored to family spice preferences.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional North Indian Meal Home Cook (Daily 2 Meals) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete North Indian Meal Home Cook (Daily 2 Meals) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.863651+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.863651+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does North Indian Meal Home Cook (Daily 2 Meals) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40735bdb-7e84-561a-bd66-3cac217acc77</t>
+          <t>1d77ddee-89f0-599a-a10b-36da34748e12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooks / Chefs Service Variation 7</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cooks / Chefs</t>
+          <t>Party &amp; Special Occasion Festival Chef</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1200</v>
+        <v>2499</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Professional home chef cooking multi-course feast (starters, biryani, gravy, sweets) for up to 15 guests.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Party &amp; Special Occasion Festival Chef procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional cooks / chefs service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Cooks / Chefs", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Party &amp; Special Occasion Festival Chef procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.866604+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.866604+00:00</t>
+          <t>[{'answer': 'The session typically takes around 240 minutes.', 'question': 'How long does Party &amp; Special Occasion Festival Chef take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ccc1f0a6-5a53-5b8f-8e95-51031f788e98</t>
+          <t>15d04ae6-56ea-505f-a737-f8f8cf9647e7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Drivers Service Variation 1</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Cooking Services</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Drivers</t>
+          <t>South Indian Breakfast &amp; Meal Cook</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>600</v>
+        <v>3299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Cook specializing in authentic idli, dosa batter, sambar, chutney, and rice meals.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional South Indian Breakfast &amp; Meal Cook procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional drivers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Drivers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete South Indian Breakfast &amp; Meal Cook procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.870149+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.870149+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does South Indian Breakfast &amp; Meal Cook take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f6b2113d-50a5-58a5-89a1-036347415a9b</t>
+          <t>d90d7615-d97a-53e2-aa2f-917d4538765a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Drivers Service Variation 2</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Drivers</t>
+          <t>Bill Payment &amp; Government Office Standing Helper</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>700</v>
+        <v>399</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Personal runner handling bank paperwork, RTO submissions, or municipal utility payments.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Bill Payment &amp; Government Office Standing Helper procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional drivers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Drivers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Bill Payment &amp; Government Office Standing Helper procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.873571+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.873571+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Bill Payment &amp; Government Office Standing Helper take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2527c933-3089-5fe2-aacd-fa3ae48c78f0</t>
+          <t>f6b2113d-50a5-58a5-89a1-036347415a9b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Drivers Service Variation 3</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Drivers</t>
+          <t>Dry Cleaning Pickup &amp; Doorstep Delivery</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Taking heavy suits, sarees, and blankets to laundry cleaner and returning ironed items.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Dry Cleaning Pickup &amp; Doorstep Delivery procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional drivers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Drivers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dry Cleaning Pickup &amp; Doorstep Delivery procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.875950+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.875950+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Dry Cleaning Pickup &amp; Doorstep Delivery take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>571bc27a-c94c-539f-ba6c-f2766e13ada2</t>
+          <t>fedc1832-7387-538a-afc3-010d00db636f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Drivers Service Variation 4</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Drivers</t>
+          <t>Event Packing &amp; Gift Wrapping Personal Assistant</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>499</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Helping families wrap wedding favors, hamper hampers, and birthday return gifts.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Event Packing &amp; Gift Wrapping Personal Assistant procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional drivers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Drivers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Event Packing &amp; Gift Wrapping Personal Assistant procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.878539+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.878539+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Event Packing &amp; Gift Wrapping Personal Assistant take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1062,945 +1098,1040 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 1</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Grocery &amp; Vegetable Market Delivery Assistant</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>600</v>
+        <v>299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Helper visiting local mandis or supermarkets to buy fresh vegetables, fruits, and provisions.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Grocery &amp; Vegetable Market Delivery Assistant procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Grocery &amp; Vegetable Market Delivery Assistant procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.880839+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.880839+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Grocery &amp; Vegetable Market Delivery Assistant take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15d04ae6-56ea-505f-a737-f8f8cf9647e7</t>
+          <t>e9557ae1-a799-5f82-b226-4287c9172840</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 2</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Pet Walking &amp; Vet Escort Assistant</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>700</v>
+        <v>349</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Escorting pets for daily walks or holding pets during veterinary vaccination visits.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Pet Walking &amp; Vet Escort Assistant procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pet Walking &amp; Vet Escort Assistant procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.883570+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.883570+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Pet Walking &amp; Vet Escort Assistant take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2aa7c0cc-9967-5a63-aa3e-d6f3b80b8304</t>
+          <t>ccc1f0a6-5a53-5b8f-8e95-51031f788e98</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 3</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Pharmacy &amp; Prescription Medicine Pickup</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>199</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Assistance runner purchasing prescribed medicines from chemist and delivering home.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Pharmacy &amp; Prescription Medicine Pickup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pharmacy &amp; Prescription Medicine Pickup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.886898+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.886898+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Pharmacy &amp; Prescription Medicine Pickup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7eacfce2-a4c4-55d7-a086-513e07cd294b</t>
+          <t>f8b1a090-ac7b-5e28-a7fc-43525597ecd7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 4</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Errand &amp; Personal Assistance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Senior Citizen Hospital Escort Helper</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>900</v>
+        <v>799</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Accompanying elderly patients to doctor appointments, wheelchair assistance, and pharmacy collection.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Senior Citizen Hospital Escort Helper procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Senior Citizen Hospital Escort Helper procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.889391+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.889391+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Senior Citizen Hospital Escort Helper take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>d90d7615-d97a-53e2-aa2f-917d4538765a</t>
+          <t>b46c4c44-3d4a-5444-8490-b358be5234b1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 5</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Babysitter &amp; Child Nanny Care</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1000</v>
+        <v>6499</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Trained nanny looking after toddlers, feeding milk/meals, diaper changes, and interactive playtime.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Babysitter &amp; Child Nanny Care procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Babysitter &amp; Child Nanny Care procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.891467+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.891467+00:00</t>
+          <t>[{'answer': 'The session typically takes around 360 minutes.', 'question': 'How long does Babysitter &amp; Child Nanny Care take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fedc1832-7387-538a-afc3-010d00db636f</t>
+          <t>8c70b4df-a510-56d3-be6f-fc7919a26797</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care Service Variation 6</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Elder Care / Patient Care</t>
+          <t>Brooming, Mopping &amp; Dusting Maid Service</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1100</v>
+        <v>1999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Daily floor sweeping, damp mopping, cobweb dusting, and trash disposal for apartment.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Brooming, Mopping &amp; Dusting Maid Service procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional elder care / patient care service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Elder Care / Patient Care", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Brooming, Mopping &amp; Dusting Maid Service procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.893865+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.893865+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Brooming, Mopping &amp; Dusting Maid Service take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>47d0dd4f-57ff-5cd3-9c81-edfd51dc96bc</t>
+          <t>a1ce921c-1580-5cc8-89c0-0c404e03620d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 1</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Cloth Washing, Folding &amp; Clothes Ironing</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>600</v>
+        <v>1799</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Operating washing machine, hanging clothes to dry, folding wardrobes, and steam ironing shirts.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Cloth Washing, Folding &amp; Clothes Ironing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Cloth Washing, Folding &amp; Clothes Ironing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.895998+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.895998+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Cloth Washing, Folding &amp; Clothes Ironing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1d77ddee-89f0-599a-a10b-36da34748e12</t>
+          <t>7eacfce2-a4c4-55d7-a086-513e07cd294b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 2</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Daily Utensil Washing &amp; Kitchen Sink Clean</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>700</v>
+        <v>1499</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Hand washing pressure cooker, non-stick pans, dishes, and wiping kitchen counter clean twice daily.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Daily Utensil Washing &amp; Kitchen Sink Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Daily Utensil Washing &amp; Kitchen Sink Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.898695+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.898695+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Daily Utensil Washing &amp; Kitchen Sink Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21214b3e-e44e-5cd7-9cec-1b17f71316af</t>
+          <t>c53f41db-6864-5098-962e-5b8cd6d01533</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 3</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Deep House Decluttering &amp; Wardrobe Organizer</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>1299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Organizing closet clothes, shoe racks, kitchen pantry, and seasonal garment storage bags.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Deep House Decluttering &amp; Wardrobe Organizer procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Deep House Decluttering &amp; Wardrobe Organizer procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.901143+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.901143+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Deep House Decluttering &amp; Wardrobe Organizer take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8c70b4df-a510-56d3-be6f-fc7919a26797</t>
+          <t>ace45992-f43f-5773-84bd-90065e6fe0ac</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 4</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Elderly Care &amp; Senior Companion Maid</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>900</v>
+        <v>6999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Kind attendant helping senior citizens with walking, medicine timely reminder, and light chores.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Elderly Care &amp; Senior Companion Maid procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Elderly Care &amp; Senior Companion Maid procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.904106+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.904106+00:00</t>
+          <t>[{'answer': 'The session typically takes around 360 minutes.', 'question': 'How long does Elderly Care &amp; Senior Companion Maid take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6415a620-9830-50c4-84ba-b4a87693725b</t>
+          <t>ab5ac2a7-edc9-5443-8456-b2f6c4ed5da9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 5</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Household Help</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Full-Day All-Round Household Helper (8 Hours)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1000</v>
+        <v>7999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Full-day maid handling cleaning, washing, grocery errands, and assisting kitchen work.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Full-Day All-Round Household Helper (8 Hours) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Full-Day All-Round Household Helper (8 Hours) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.906356+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.906356+00:00</t>
+          <t>[{'answer': 'The session typically takes around 480 minutes.', 'question': 'How long does Full-Day All-Round Household Helper (8 Hours) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01d0d750-e8bf-58e1-bd31-8ff6ad447a4a</t>
+          <t>7986b1ac-f5d8-5ae3-8a37-dcc3c6f0dc6e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 6</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Barbecue &amp; Grill Party Master</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1100</v>
+        <v>2999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Outdoor live charcoal grill chef marinating and grilling paneer tikka, chicken tandoori, and veggies.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Barbecue &amp; Grill Party Master procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Barbecue &amp; Grill Party Master procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.908696+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.908696+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Barbecue &amp; Grill Party Master take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7986b1ac-f5d8-5ae3-8a37-dcc3c6f0dc6e</t>
+          <t>40b63594-5545-5186-8c79-12e95f135bbd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers Service Variation 7</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maids / Housekeepers</t>
+          <t>Biryani &amp; Mughlai Special Home Chef</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>2999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Master chef specialized in Dum Biryani, Kebabs, Gravy, and authentic Phirni.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Biryani &amp; Mughlai Special Home Chef procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional maids / housekeepers service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Maids / Housekeepers", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Biryani &amp; Mughlai Special Home Chef procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.911450+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.911450+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Biryani &amp; Mughlai Special Home Chef take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>e9557ae1-a799-5f82-b226-4287c9172840</t>
+          <t>50708bc9-4abb-563d-92a7-3266f4eb4213</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 1</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Chinese &amp; Pan-Asian Dimsum Chef</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>600</v>
+        <v>2599</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wok master preparing Hakka noodles, Manchurian, momos, and Thai curries.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Chinese &amp; Pan-Asian Dimsum Chef procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Chinese &amp; Pan-Asian Dimsum Chef procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.913490+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.913490+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Chinese &amp; Pan-Asian Dimsum Chef take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>78d97bd8-a6b1-5ce8-abc4-8f2bd1ab6794</t>
+          <t>47d0dd4f-57ff-5cd3-9c81-edfd51dc96bc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 2</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Continental &amp; Italian Pasta Specialist</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>700</v>
+        <v>2799</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Gourmet chef preparing fresh hand-rolled pasta, wood-fire style pizza, and risotto at home.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Continental &amp; Italian Pasta Specialist procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Continental &amp; Italian Pasta Specialist procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.915701+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.915701+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Continental &amp; Italian Pasta Specialist take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b46c4c44-3d4a-5444-8490-b358be5234b1</t>
+          <t>78d97bd8-a6b1-5ce8-abc4-8f2bd1ab6794</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 3</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Gluten-Free &amp; Organic Health Chef</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>800</v>
+        <v>3599</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Certified nutritionist-chef preparing millet rotis, quinoa salads, and sugar-free desserts.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Gluten-Free &amp; Organic Health Chef procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Gluten-Free &amp; Organic Health Chef procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.918568+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.918568+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Gluten-Free &amp; Organic Health Chef take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24122f06-e74f-584d-83f0-8e07ffcc566e</t>
+          <t>571bc27a-c94c-539f-ba6c-f2766e13ada2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 4</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Home Bakery &amp; Cake Baking Assistant</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>900</v>
+        <v>1999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Baking expert assisting with fresh birthday cakes, brownies, cupcakes, and artisanal bread.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Home Bakery &amp; Cake Baking Assistant procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Home Bakery &amp; Cake Baking Assistant procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.921072+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.921072+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Home Bakery &amp; Cake Baking Assistant take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ace45992-f43f-5773-84bd-90065e6fe0ac</t>
+          <t>6f70225a-efcb-50ac-a11a-3abf2809908d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 5</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Seafood &amp; Coastal Recipe Specialist</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1000</v>
+        <v>3199</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Chef crafting Goan, Malabari, or Bengali fish curry, prawn fry, and crab masala.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Seafood &amp; Coastal Recipe Specialist procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Seafood &amp; Coastal Recipe Specialist procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.923398+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.923398+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Seafood &amp; Coastal Recipe Specialist take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f8b1a090-ac7b-5e28-a7fc-43525597ecd7</t>
+          <t>6415a620-9830-50c4-84ba-b4a87693725b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters Service Variation 6</t>
+          <t>7. Domestic Help &amp; Cooking</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7. Domestic Help &amp; Cooking</t>
+          <t>Specialized Cooking</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nannies / Babysitters</t>
+          <t>Traditional Indian Sweet Halwai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1100</v>
+        <v>3499</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Expert sweet maker preparing Gulab Jamun, Rasgulla, Kaju Katli, and Jalebi for family functions.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Initial consultation and assessment", "Professional service execution", "Basic background verified personnel", "Service guarantee"]</t>
+          <t>['Professional Traditional Indian Sweet Halwai procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nannies / babysitters service for your household needs.", "type": "description"}, {"type": "highlights", "items": ["Experienced Nannies / Babysitters", "Background verified", "Punctual and reliable", "Replacement guarantee"]}, {"type": "excluded_scope", "items": ["Cost of groceries or special equipment", "Transportation costs for special errands"]}, {"type": "process_steps", "steps": [{"title": "Requirement Gathering", "description": "Understanding specific household needs", "step_number": 1}, {"title": "Personnel Matching", "description": "Assigning the right professional for the task", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out the requested domestic duties", "step_number": 3}, {"title": "Quality Check", "description": "Ensuring the service meets SmartServe standards", "step_number": 4}, {"title": "Feedback", "description": "Collecting customer feedback for continuous improvement", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Provide clear instructions for future visits", "Maintain communication regarding preferences"]}, {"type": "tools_materials", "tools": ["Standard household cleaning tools", "Basic cooking utensils (provided by customer)"], "materials": []}, {"type": "customer_setup", "requirements": ["Provide access to the premises", "Ensure a safe working environment", "Provide necessary groceries/materials"]}, {"type": "expected_results", "items": "Reliable and high-quality domestic assistance."}, {"type": "important_notes", "items": "All personnel are background verified for safety and security."}, {"type": "warranty", "details": "Satisfaction guarantee; replacement provided if unsatisfied.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all our domestic helpers undergo strict background verification.", "question": "Are the professionals background checked?"}, {"answer": "We offer a replacement guarantee to ensure you get the right match.", "question": "What if I am not satisfied with the service?"}, {"answer": "No, it is not mandatory to provide meals.", "question": "Do I need to provide meals for the helper?"}, {"answer": "Yes, you can request recurring services with the same professional.", "question": "Can I request the same professional every time?"}]}, {"type": "tips", "items": ["Communicate your specific preferences clearly on the first day."]}, {"dos": ["Provide a safe and respectful working environment."], "type": "dos_donts", "donts": ["Do not request services outside the agreed scope."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Traditional Indian Sweet Halwai procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.926098+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:37:11.926098+00:00</t>
+          <t>[{'answer': 'The session typically takes around 240 minutes.', 'question': 'How long does Traditional Indian Sweet Halwai take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
